--- a/output/xlsx/CRUDUsers--GT-.xlsx
+++ b/output/xlsx/CRUDUsers--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="74">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -107,28 +107,22 @@
     <t>exibe lista completa de usuários</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe pagina com campos de cadastro do usuario</t>
-  </si>
-  <si>
-    <t>exibe pagina com campos de cadastro do usuario</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe mensagem indicando que novo usuario foi criado</t>
-  </si>
-  <si>
-    <t>exibe mensagem indicando que novo usuario foi criado</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe lista completa de usuarios</t>
-  </si>
-  <si>
-    <t>exibe lista completa de usuarios</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe dados do usuario</t>
-  </si>
-  <si>
-    <t>exibe dados do usuario</t>
+    <t>system: SYSTEM: exibe página com campos de cadastro do usuário</t>
+  </si>
+  <si>
+    <t>exibe página com campos de cadastro do usuário</t>
+  </si>
+  <si>
+    <t>system: SYSTEM: exibe mensagem indicando que novo usuário foi criado</t>
+  </si>
+  <si>
+    <t>exibe mensagem indicando que novo usuário foi criado</t>
+  </si>
+  <si>
+    <t>system: SYSTEM: exibe dados do usuário</t>
+  </si>
+  <si>
+    <t>exibe dados do usuário</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -140,10 +134,10 @@
     <t>Alternative Flow 1: Usuário com login repetido</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe mensagem informando que os este usuarios já existe</t>
-  </si>
-  <si>
-    <t>exibe mensagem informando que os este usuarios já existe</t>
+    <t>system: SYSTEM: exibe mensagem informando que os este usuários já existe</t>
+  </si>
+  <si>
+    <t>exibe mensagem informando que os este usuários já existe</t>
   </si>
   <si>
     <t>TC4</t>
@@ -158,10 +152,10 @@
     <t>exibe campos do documento com valores atuais que podem ser editados</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe novos dados do usuarios</t>
-  </si>
-  <si>
-    <t>exibe novos dados do usuarios</t>
+    <t>system: SYSTEM: exibe novos dados do usuários</t>
+  </si>
+  <si>
+    <t>exibe novos dados do usuários</t>
   </si>
   <si>
     <t>TC5</t>
@@ -170,10 +164,10 @@
     <t>Alternative Flow 4: Edita dados e altera linguagem</t>
   </si>
   <si>
-    <t>system: SYSTEM: e apresentado na nova linguagem</t>
-  </si>
-  <si>
-    <t>e apresentado na nova linguagem</t>
+    <t>system: SYSTEM: é apresentado na nova linguagem</t>
+  </si>
+  <si>
+    <t>é apresentado na nova linguagem</t>
   </si>
   <si>
     <t>TC6</t>
@@ -182,46 +176,40 @@
     <t>Alternative Flow 5: Reseta senha</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe mensagem pedindo confirmacao</t>
-  </si>
-  <si>
-    <t>exibe mensagem pedindo confirmacao</t>
+    <t>system: SYSTEM: exibe mensagem pedindo confirmação</t>
+  </si>
+  <si>
+    <t>exibe mensagem pedindo confirmação</t>
   </si>
   <si>
     <t>TC7</t>
   </si>
   <si>
-    <t>Alternative Flow 6: Bloqueio de usuario</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe mensagem confirmando bloqueio de usuario</t>
-  </si>
-  <si>
-    <t>exibe mensagem confirmando bloqueio de usuario</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe lista completa de usuários onde o usuario atualizado e sinalizado como bloqueado</t>
-  </si>
-  <si>
-    <t>exibe lista completa de usuários onde o usuario atualizado e sinalizado como bloqueado</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe mensagem pedindo confirmação</t>
-  </si>
-  <si>
-    <t>exibe mensagem pedindo confirmação</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe mensagem confirmando desbloqueio de usuario</t>
-  </si>
-  <si>
-    <t>exibe mensagem confirmando desbloqueio de usuario</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe lista completa de usuários onde o usuario atualizado nao e sinalizado como bloqueado</t>
-  </si>
-  <si>
-    <t>exibe lista completa de usuários onde o usuario atualizado nao e sinalizado como bloqueado</t>
+    <t>Alternative Flow 6: Bloqueio de usuário</t>
+  </si>
+  <si>
+    <t>system: SYSTEM: exibe mensagem confirmando bloqueio de usuário</t>
+  </si>
+  <si>
+    <t>exibe mensagem confirmando bloqueio de usuário</t>
+  </si>
+  <si>
+    <t>system: SYSTEM: exibe lista completa de usuários onde o usuário atualizado é sinalizado como bloqueado</t>
+  </si>
+  <si>
+    <t>exibe lista completa de usuários onde o usuário atualizado é sinalizado como bloqueado</t>
+  </si>
+  <si>
+    <t>system: SYSTEM: exibe mensagem confirmando desbloqueio de usuário</t>
+  </si>
+  <si>
+    <t>exibe mensagem confirmando desbloqueio de usuário</t>
+  </si>
+  <si>
+    <t>system: SYSTEM: exibe lista completa de usuários onde o usuário atualizado não é sinalizado como bloqueado</t>
+  </si>
+  <si>
+    <t>exibe lista completa de usuários onde o usuário atualizado não é sinalizado como bloqueado</t>
   </si>
   <si>
     <t>TC10</t>
@@ -230,22 +218,22 @@
     <t>Alternative Flow 9: Test de bloqueio</t>
   </si>
   <si>
-    <t>system: SYSTEM: exibe mensagem que usuário esta bloqueado</t>
-  </si>
-  <si>
-    <t>exibe mensagem que usuário esta bloqueado</t>
+    <t>system: SYSTEM: exibe mensagem que usuário está bloqueado</t>
+  </si>
+  <si>
+    <t>exibe mensagem que usuário está bloqueado</t>
   </si>
   <si>
     <t>TC11</t>
   </si>
   <si>
-    <t>Alternative Flow 10: Deleta usuario</t>
-  </si>
-  <si>
-    <t>system: SYSTEM: exibe mensagem solicitando confirmacao</t>
-  </si>
-  <si>
-    <t>exibe mensagem solicitando confirmacao</t>
+    <t>Alternative Flow 10: Deleta usuário</t>
+  </si>
+  <si>
+    <t>system: SYSTEM: exibe mensagem solicitando confirmação</t>
+  </si>
+  <si>
+    <t>exibe mensagem solicitando confirmação</t>
   </si>
 </sst>
 </file>
@@ -525,13 +513,13 @@
         <v>5.0</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D14" t="s" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s" s="3">
         <v>27</v>
@@ -545,13 +533,13 @@
         <v>6.0</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D15" t="s" s="3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s" s="3">
         <v>27</v>
@@ -565,13 +553,13 @@
         <v>7.0</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D16" t="s" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s" s="3">
         <v>27</v>
@@ -582,7 +570,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s" s="0">
         <v>27</v>
@@ -593,7 +581,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s" s="1">
         <v>13</v>
@@ -607,7 +595,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s" s="1">
         <v>17</v>
@@ -646,13 +634,13 @@
         <v>1.0</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D24" t="s" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s" s="3">
         <v>27</v>
@@ -663,7 +651,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s" s="0">
         <v>27</v>
@@ -674,7 +662,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="1">
         <v>13</v>
@@ -688,7 +676,7 @@
         <v>15</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E29" t="s" s="1">
         <v>17</v>
@@ -727,13 +715,13 @@
         <v>1.0</v>
       </c>
       <c r="B32" t="s" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D32" t="s" s="3">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s" s="3">
         <v>27</v>
@@ -747,13 +735,13 @@
         <v>2.0</v>
       </c>
       <c r="B33" t="s" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D33" t="s" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s" s="3">
         <v>27</v>
@@ -764,7 +752,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s" s="0">
         <v>27</v>
@@ -775,7 +763,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s" s="1">
         <v>13</v>
@@ -789,7 +777,7 @@
         <v>15</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E38" t="s" s="1">
         <v>17</v>
@@ -828,13 +816,13 @@
         <v>1.0</v>
       </c>
       <c r="B41" t="s" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D41" t="s" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E41" t="s" s="3">
         <v>27</v>
@@ -848,13 +836,13 @@
         <v>2.0</v>
       </c>
       <c r="B42" t="s" s="3">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D42" t="s" s="3">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E42" t="s" s="3">
         <v>27</v>
@@ -865,7 +853,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s" s="0">
         <v>27</v>
@@ -876,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="B46" t="s" s="0">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s" s="1">
         <v>13</v>
@@ -890,7 +878,7 @@
         <v>15</v>
       </c>
       <c r="B47" t="s" s="0">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E47" t="s" s="1">
         <v>17</v>
@@ -929,13 +917,13 @@
         <v>1.0</v>
       </c>
       <c r="B50" t="s" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D50" t="s" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E50" t="s" s="3">
         <v>27</v>
@@ -949,13 +937,13 @@
         <v>2.0</v>
       </c>
       <c r="B51" t="s" s="3">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C51" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D51" t="s" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E51" t="s" s="3">
         <v>27</v>
@@ -966,7 +954,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B52" t="s" s="0">
         <v>27</v>
@@ -977,7 +965,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s" s="0">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C55" t="s" s="1">
         <v>13</v>
@@ -991,7 +979,7 @@
         <v>15</v>
       </c>
       <c r="B56" t="s" s="0">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E56" t="s" s="1">
         <v>17</v>
@@ -1030,13 +1018,13 @@
         <v>1.0</v>
       </c>
       <c r="B59" t="s" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D59" t="s" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E59" t="s" s="3">
         <v>27</v>
@@ -1050,13 +1038,13 @@
         <v>2.0</v>
       </c>
       <c r="B60" t="s" s="3">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D60" t="s" s="3">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E60" t="s" s="3">
         <v>27</v>
@@ -1070,13 +1058,13 @@
         <v>3.0</v>
       </c>
       <c r="B61" t="s" s="3">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C61" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D61" t="s" s="3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E61" t="s" s="3">
         <v>27</v>
@@ -1090,13 +1078,13 @@
         <v>4.0</v>
       </c>
       <c r="B62" t="s" s="3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C62" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D62" t="s" s="3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E62" t="s" s="3">
         <v>27</v>
@@ -1110,13 +1098,13 @@
         <v>5.0</v>
       </c>
       <c r="B63" t="s" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C63" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D63" t="s" s="3">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E63" t="s" s="3">
         <v>27</v>
@@ -1130,13 +1118,13 @@
         <v>6.0</v>
       </c>
       <c r="B64" t="s" s="3">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C64" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D64" t="s" s="3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E64" t="s" s="3">
         <v>27</v>
@@ -1150,13 +1138,13 @@
         <v>7.0</v>
       </c>
       <c r="B65" t="s" s="3">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C65" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D65" t="s" s="3">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E65" t="s" s="3">
         <v>27</v>
@@ -1170,13 +1158,13 @@
         <v>8.0</v>
       </c>
       <c r="B66" t="s" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C66" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D66" t="s" s="3">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E66" t="s" s="3">
         <v>27</v>
@@ -1187,7 +1175,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B67" t="s" s="0">
         <v>27</v>
@@ -1198,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="B70" t="s" s="0">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C70" t="s" s="1">
         <v>13</v>
@@ -1212,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="B71" t="s" s="0">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E71" t="s" s="1">
         <v>17</v>
@@ -1251,13 +1239,13 @@
         <v>1.0</v>
       </c>
       <c r="B74" t="s" s="3">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C74" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D74" t="s" s="3">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E74" t="s" s="3">
         <v>27</v>
@@ -1268,7 +1256,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B75" t="s" s="0">
         <v>27</v>
@@ -1279,7 +1267,7 @@
         <v>11</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C78" t="s" s="1">
         <v>13</v>
@@ -1293,7 +1281,7 @@
         <v>15</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E79" t="s" s="1">
         <v>17</v>
@@ -1332,13 +1320,13 @@
         <v>1.0</v>
       </c>
       <c r="B82" t="s" s="3">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C82" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D82" t="s" s="3">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E82" t="s" s="3">
         <v>27</v>
@@ -1349,7 +1337,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="1">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B83" t="s" s="0">
         <v>27</v>

--- a/output/xlsx/CRUDUsers--GT-.xlsx
+++ b/output/xlsx/CRUDUsers--GT-.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Deve existir pelo menos um usuário super administrador</t>
+    <t>Deve existir pelo menos um usuário cadastrado</t>
   </si>
   <si>
     <t>#</t>
